--- a/artfynd/A 46436-2025 artfynd.xlsx
+++ b/artfynd/A 46436-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,19 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>116571658</v>
+        <v>116530099</v>
       </c>
       <c r="B2" t="n">
-        <v>57294</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -717,7 +712,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -731,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>795677</v>
+        <v>795751</v>
       </c>
       <c r="R2" t="n">
-        <v>7282327</v>
+        <v>7282369</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -771,7 +766,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>färska hackspår på en gran</t>
+          <t>tydlig hackspår, äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -808,19 +803,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>116573469</v>
+        <v>116530594</v>
       </c>
       <c r="B3" t="n">
-        <v>57294</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -864,10 +854,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>795750</v>
+        <v>795699</v>
       </c>
       <c r="R3" t="n">
-        <v>7282021</v>
+        <v>7282367</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -904,7 +894,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>äldre hackspår</t>
+          <t>äldre hackspår på barken av en tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -938,6 +928,601 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>116571658</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Brännträsk, Lustgårdens nat. res., Nb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>795677</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7282327</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Norrfjärden</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-04-19</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-04-19</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>färska hackspår på en gran</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>boreal blandskog: tall, gran, björk, sälg, asp, blåbärsbuskar osv.</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Corina Delling</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Corina Delling</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>116573469</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Brännträsk, Lustgårdens nat. res., Nb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>795750</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7282021</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Norrfjärden</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-04-19</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-04-19</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>äldre hackspår</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>boreal blandskog: tall, gran, björk, sälg, asp, blåbärsbuskar osv.</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Corina Delling</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Corina Delling</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>116598553</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Spår Spillkråka, Lustgårdens nat. res., Nb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>795737</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7282369</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Norrfjärden</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-04-19</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-04-19</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anne Rebotzke</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anne Rebotzke</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>116599876</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Spår tjäder &amp; järpe, Lustgårdens nat. res., Nb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>795811</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7281943</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Norrfjärden</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-04-19</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-04-19</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anne Rebotzke</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anne Rebotzke</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>116599446</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Talltita, Nb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>795734</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7282252</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Norrfjärden</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-04-19</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-04-19</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anne Rebotzke</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anne Rebotzke</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 46436-2025 artfynd.xlsx
+++ b/artfynd/A 46436-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -800,6 +805,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116530099</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -928,6 +938,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116530594</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1056,6 +1071,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116571658</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1184,6 +1204,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116573469</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1289,6 +1314,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116598553</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1402,6 +1432,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116599876</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1523,8 +1558,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116599446</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>